--- a/AAII_Financials/Quarterly/CTTAY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CTTAY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="92">
   <si>
     <t>CTTAY</t>
   </si>
@@ -656,177 +656,181 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -869,86 +873,89 @@
       <c r="P8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R8" s="3">
         <v>11398200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11234500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>10276100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>10095700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>9534700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>8658800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>8839000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>9072700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>9096800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>8656500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>6173800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>9169600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>12916600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13601600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>13251000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13214100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>13284100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12760900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12597600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12091900</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>12660400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>11997100</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>12378900</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>12911800</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>12353200</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>11719100</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,86 +998,89 @@
       <c r="P9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R9" s="3">
         <v>9202300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>8926300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8670600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>7933300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>7624600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>6738500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>6687200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>6785900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>6826900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>6359000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>5154300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>7009600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>9999600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>10350800</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>10027000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>9993800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>10021800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>9664900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>9342600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>9027500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>9366800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>8917900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>9203800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>9549200</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>9114300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>8696900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1113,86 +1123,89 @@
       <c r="P10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R10" s="3">
         <v>2195900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2308300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>1605500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>2162400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1910100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1920300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>2151800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>2286800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>2269900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>2297500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1019500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>2160000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2917000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>3250800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>3223900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>3220300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>3262300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>3096000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>3255000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>3064400</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>3293600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>3079200</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>3175100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>3362600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3238900</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>3022200</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1279,86 +1293,89 @@
       <c r="P12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="Q12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R12" s="3">
         <v>1186600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>1127300</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>1056100</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>1057400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>1066600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>910600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>935000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>864600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>914600</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>786300</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>841000</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>956300</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>1301200</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>1377300</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>1352900</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>1295400</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>1291500</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>1282900</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>1193300</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>1127100</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>837900</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>872300</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>896100</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>916400</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>751800</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>854700</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
@@ -1523,8 +1543,8 @@
       <c r="P14" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1645,8 +1668,8 @@
       <c r="P15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,8 +1790,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
@@ -1808,86 +1835,89 @@
       <c r="P17" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R17" s="3">
         <v>10809100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>11221300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>10455200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>9687400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9218100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>8208100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>8338800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>8371600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>8746100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>9328400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>6832500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>8626600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>12769900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>16015400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>12364800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>12229200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>12056400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>11753500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>11358200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>10972900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>11250500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>10833000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>11108500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>11579400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>10933800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>11019100</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
@@ -1930,86 +1960,89 @@
       <c r="P18" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R18" s="3">
         <v>589100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>13200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-179100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>408400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>316600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>450700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>500100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>701000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>350700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-671800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-658700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>543100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>146600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-2413800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>886200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>984800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1227700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>1007400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>1239400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>1119100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>1409900</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>1164100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1270400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>1332400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>1419400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>699900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
@@ -2096,86 +2130,89 @@
       <c r="P20" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R20" s="3">
         <v>70200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-35200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>11900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-36400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-40700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>129300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-28000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-17400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA20" s="3">
-        <v>0</v>
-      </c>
       <c r="AB20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3">
         <v>108900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-73100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>18600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>32500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>20100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>61900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>30400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>17600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-74200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>12100</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-13200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-13400</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>31800</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>29000</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
@@ -2218,86 +2255,89 @@
       <c r="P21" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R21" s="3">
         <v>1295700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1130500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>918000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1026300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>920800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1009500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>1247500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1395700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1239500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>716700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>127900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1441900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1091100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>1304100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>1746400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>1782900</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>1968100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>1700400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>1840600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>1725000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>1951900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>1787300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>1840700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1909900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2099400</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>1293700</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
@@ -2340,86 +2380,89 @@
       <c r="P22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="3">
         <v>66800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>68700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>68300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>52300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>10000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>57000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>63700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>61500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>74500</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>67600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>67000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>65800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>115300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>93200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>84800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>84100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>94600</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>76500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>74400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>70600</v>
       </c>
-      <c r="AK22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="AL22" s="3">
+      <c r="AL22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="AM22" s="3">
         <v>74700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>76700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>84700</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>82800</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>58300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2462,86 +2505,89 @@
       <c r="P23" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R23" s="3">
         <v>592600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-90800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-252800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>367900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>270200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>353000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>565700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>611500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>258800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-745600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-725700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>586100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-41800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-2488400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>833800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>920800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1195000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>961200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>1169800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>1066000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>1335700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>1101500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>1180400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>1234300</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>1368400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>670600</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2584,86 +2630,89 @@
       <c r="P24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R24" s="3">
         <v>256000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>123200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>97700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>103000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>69800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>76700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>134600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>66300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-110300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-151900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>145100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>279700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-65500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>251600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>218200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>325800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>208700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>244100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>240900</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>459800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>269300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>326200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>336900</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>416000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>205800</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,8 +2833,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2828,86 +2880,89 @@
       <c r="P26" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R26" s="3">
         <v>336600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-214000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-263300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>270200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>167200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>283200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>489000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>476900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>192500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-635200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-573800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>441100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-321500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2422900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>582200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>702600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>869200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>752600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>925700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>825100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>875900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>832200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>854300</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>897400</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>952400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>464800</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2950,86 +3005,89 @@
       <c r="P27" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R27" s="3">
         <v>319700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-227800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-272800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>260600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>144400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>274000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>470600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>471800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>169200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-651200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-577700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>440900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-348600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2433300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>570300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>688100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>841600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>740600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>910600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>809900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>853300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>818000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>836300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>879900</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>921700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>444300</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3206,38 +3267,38 @@
       <c r="T29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
         <v>58900</v>
       </c>
-      <c r="W29" s="3">
+      <c r="X29" s="3">
         <v>106300</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>1800</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>36500</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>-66200</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-230700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-122100</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
+      <c r="AE29" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="AF29" s="3">
         <v>0</v>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,86 +3630,89 @@
       <c r="P32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R32" s="3">
         <v>-70200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>35200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-11900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>36400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>40700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-129300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>28000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>17400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>6100</v>
       </c>
-      <c r="AA32" s="3">
-        <v>0</v>
-      </c>
       <c r="AB32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-108900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>73100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-18600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-32500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-20100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-61900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-30400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-17600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>74200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-12100</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>13200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>13400</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-31800</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-29000</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3682,86 +3755,89 @@
       <c r="P33" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R33" s="3">
         <v>319700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-227800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-272800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>260600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>144400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>332900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>576900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>473600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>205700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-717400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-808500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>318900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-348600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2433300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>570300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>688100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>841600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>740600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>910600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>809900</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>853300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>818000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>836300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>879900</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>921700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>444300</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,8 +3958,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3926,213 +4005,219 @@
       <c r="P35" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R35" s="3">
         <v>319700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-227800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-272800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>260600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>144400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>332900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>576900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>473600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>205700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-717400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-808500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>318900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-348600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2433300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>570300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>688100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>841600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>740600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>910600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>809900</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>853300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>818000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>836300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>879900</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>921700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>444300</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>931100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1594600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1764700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1608600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2338200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1808300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3070700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2376800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2321900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2534300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3230900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2358100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2479800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2446900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3309500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2439400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2075400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2528600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2459900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2461700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2288200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3035200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2931100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2509000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2678800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2787300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3901300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2414700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2101400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2173000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3266500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1918300</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2360800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2512900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2111000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1717700</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2026800</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>2225200</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>2473200</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>1690200</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4386,939 +4476,963 @@
         <v>0</v>
       </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>155100</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>148900</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>145900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>150700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>128400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>132900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>136700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>190100</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>146400</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>148300</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>161200</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>124900</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>138300</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>136800</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>140300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>121100</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>379400</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>178500</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>385600</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>356100</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>594100</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>617100</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>601200</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>568800</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>534700</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>567700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3394300</v>
+      </c>
+      <c r="E43" s="3">
         <v>4598200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4345400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4919600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>4594200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4299600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8429400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>9383200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>8626400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>8982600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9535800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9641700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9527700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9601900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>9021500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>10484500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>9371300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>8953100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>8116500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>8216700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>6838300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>7153000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>7687100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>8325700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>7555100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>8407800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>9387400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>11151300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>10451700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>10685700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>9353800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>10664300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>9453300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>9302400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8804800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>9477100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>9112700</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>9974700</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>8824000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>9078500</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2944100</v>
+      </c>
+      <c r="E44" s="3">
         <v>3653900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3601000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3882400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>4245400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3957000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>6328800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>7183800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>7006300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>6955400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6937100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7283200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>7712800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>7816100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>7453700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>7507700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>6849800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>6052300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5413700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>5316200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>4812200</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>4387800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>4227200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>4415900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>5287300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>5637600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>5480300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>6172600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>5817100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>5855800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>5348000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>5547800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>5036500</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>4795000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>4631800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>4887300</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>4755700</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>4832000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>4405500</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>4555100</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5491800</v>
+      </c>
+      <c r="E45" s="3">
         <v>713700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1283300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>1829200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22218400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20913300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>453500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1554800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1602900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1551400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>569200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1510800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1604700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1503700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1257500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1407400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1450900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1433700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1286500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1483300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>9138200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>8174500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1485400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1527200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>1738700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1728500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1923700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2106100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>2032300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1971000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1509400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>1670100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>1667000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>1592000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>1139300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>1164600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>1238000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>1346500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>1198200</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>1221600</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12761300</v>
+      </c>
+      <c r="E46" s="3">
         <v>10560400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11127200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12239800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>33396400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>30978200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>18583700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>20498600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>19557500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>20023700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>20546000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>20793800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>21325000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>21368500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>21197200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>21987900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>19893300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>19118500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>17405000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>17610900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>23213600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>22940700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>16477100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>16926100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>17421200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>18686100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>20830900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>21981600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>20542900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>20806500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>19857000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>19979100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>18903200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>18558300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>17281000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>17863800</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>17734300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>18947200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>17435700</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>17113000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>99400</v>
+      </c>
+      <c r="E47" s="3">
         <v>119900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>122100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>124400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>146800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>111300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>449300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>501900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>505700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>461800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>460900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>459800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>484900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>465000</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>825300</v>
       </c>
       <c r="R47" s="3">
         <v>825300</v>
       </c>
       <c r="S47" s="3">
+        <v>825300</v>
+      </c>
+      <c r="T47" s="3">
         <v>824800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>798900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>764200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>681500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>800700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>677500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>634000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>671300</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>737600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>760800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>828900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>897100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>1147600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>1162800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>1087400</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>1071000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>823700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>744100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>599800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>579400</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>564100</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>580800</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>580200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>559900</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5840300</v>
+      </c>
+      <c r="E48" s="3">
         <v>7135900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>6053800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>7092600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7376400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6906600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>10293000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>12696900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>12407600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>12622700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10808000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>12209600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>12471000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>12395300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>12713800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>12376200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>12244100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>12526000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>12384300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>11853500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>11746600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>11908500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>13737000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>13674400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>15396000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>15707700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>17446200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>18065800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>17087100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>17199100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14653200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13812400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>12664600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>12256500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>12580400</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>12043600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>11988500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>12650300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>12381800</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>11559200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>478700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1131100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1136600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1152200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1340000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1298100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3808900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4298500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4223700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4293900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4272100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4320700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4487100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4477500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4642900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4671600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>5168900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>5209300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>5203100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>5038500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4996100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5057500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5693700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5874900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>7336200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>7362400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>7944600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>8349000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>10649000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>10763500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>10409200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>10102700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9447300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9322700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>9668600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>9313200</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>9443000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>10091900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>9826400</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>9313400</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>110800</v>
+      </c>
+      <c r="E52" s="3">
         <v>170600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>1330300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>161900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>236100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>255100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>2305600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>510800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>527200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>557800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2574300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>544000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>581200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>634500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2628300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>2463100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2692100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2757400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>2880800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3047800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>2948900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>2894700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>2993100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>2714500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2584900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2488100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2644000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2807200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2248100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2206300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1836100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1918400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1777700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1769300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1878000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>2119100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>2093900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>2231100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>2238300</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>2531900</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>20075400</v>
+      </c>
+      <c r="E54" s="3">
         <v>20159100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>20890000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>21806900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>43713400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>40378300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38271000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>41259200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>39884300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>40763800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>41729900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>40692600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>41763800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>41685100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>42007600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>42324200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>40823100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>40410000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>38637400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>38232200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>43705800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>43478900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>39534900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>39861200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>43475800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>45005200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>49694500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>52100700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>51674700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>52138200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>47842900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>46883500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>43616500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>42650900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>42007900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>41919000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>41823700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>44501200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>42462500</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>41077400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1998200</v>
+      </c>
+      <c r="E57" s="3">
         <v>2648400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2758000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2708000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2958300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2870700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>6699500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>6853700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6842400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>7104300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>7599200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7147800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7577400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>8005400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8458700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7764100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>7361500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>7085400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>6358700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>5789600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>5429700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>5224300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>5917700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>5993100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>4933700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>7339400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>8301500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>8414000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>8183400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>8596000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>8626900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>8300100</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>7630700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>7419200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>7627800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>7146900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>7414800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>7935100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>7334000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>7039500</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3158900</v>
+      </c>
+      <c r="E58" s="3">
         <v>2921700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2436300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2880400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>2694100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2827500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2895700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3531100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>3997600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>3427600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2920300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4041800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4502000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4378300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>4085600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>4653900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>3133200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2225900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1753300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>2127500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1974700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1908500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2184300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2562100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3737100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3940400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4954300</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5579500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>5735900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4767100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3735500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3970600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>4090300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3290400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>2325000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3310400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>2912200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3580600</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>3915700</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>4349200</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3487900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1986600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1652000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>2896900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21773300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11838500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2157600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>4356500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>4003000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3927100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>2992200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4555800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4434300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4382100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6098600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6487600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6364500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5668600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5593400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5923600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>11793700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>10044900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>6116800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5991700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5821500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>6025200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>6439800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>6928400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>6188000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>6791700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>6225600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>6303600</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>5830500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>6214500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>5966700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>5992100</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>5746800</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>5243600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>4660400</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>4838300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9224300</v>
+      </c>
+      <c r="E60" s="3">
         <v>8433100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8683800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9286600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>28224300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>18396000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14772800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>16379700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>16329200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>16209900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>16728200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>17268600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>17903100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>18359800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>18642900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>18905500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>16859200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14979900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>13705400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>13840700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>19198000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>17177700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>14218700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>14546900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>14492400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>17305000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>19695500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>20921800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>20107300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>20154800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>18588000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>18574300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>17551500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>16924000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>15919600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>16449400</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>16073900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>16759300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>15910100</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>16227000</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4695500</v>
+      </c>
+      <c r="E61" s="3">
         <v>4700800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>5578300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6027200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7309500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4324500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4257200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5051300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4565500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4972500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5005000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4563200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4858400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>4326700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>4437000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>4538000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5099300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5011900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5033700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>4946500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4963600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5287400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5131000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5125100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5691500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>3526900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>3940200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>3770400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>3285900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2780300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1714000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1717700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1618000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1602800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>2264000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>2255600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>3099400</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>3391600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>3405000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>2622600</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>173700</v>
+      </c>
+      <c r="E62" s="3">
         <v>256000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>233700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>191200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>193800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>200000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>556000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>772900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>762900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>761700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>796900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>778800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>710800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>737900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3714800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>2927200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3220400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5489700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>6164400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>6208400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6305800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6277100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7578900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>7587800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>7564400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>7250800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>7525400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>7918000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>6978800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>6468200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>5854400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>5677300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>5576200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>5445600</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>5546800</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>5600300</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>5613400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>5895200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>5851600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>6269400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>15064500</v>
+      </c>
+      <c r="E66" s="3">
         <v>14857600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>16008000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>16971700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>37322400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>24381800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>22950600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25423800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>24733700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25322000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>26116900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>25267500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26573300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26412500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>27321700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>26876900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>25671100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>25983600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>25394100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>25441400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>30887600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>29142500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>27304400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>27640100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>28235300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>28573400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>31721900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>33183400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>30906600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>30000900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>26727600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>26519400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>25261800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>24475400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>24248600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>24806800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>25289100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>26599100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>25712200</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>25636400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3579300</v>
+      </c>
+      <c r="E72" s="3">
         <v>3919100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3750100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3727600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3439800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>12485900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>11890500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>12329900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>11335000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>11559000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>11901200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>11113400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>11136800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11182900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>15579600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>14889300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>15199500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13869200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>15653900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>15357900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>15839400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>17524000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>16073900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>15868100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>18795200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>19603700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>20637100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>22020900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>23484200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>24435900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>23483900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>22642200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>20507500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>20415400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>19999400</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>19146100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>18328000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>19297300</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>18417400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>17495800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4800600</v>
+      </c>
+      <c r="E76" s="3">
         <v>5040900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4619000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4582900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5947200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15528500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>14857600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>15344600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>14687700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>14971400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>15116600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>14946800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>14703600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>14762800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14685900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>15447300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>15152000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>14426400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>13243400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>12790800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>12818200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>14336400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>12230500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>12221000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>15240600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>16431700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>17972600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>18917300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>20768000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>22137200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>21115200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>20364100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>18354700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>18175500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>17759300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>17112300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>16534700</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>17902100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>16750300</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>15441000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,135 +8688,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8670,86 +8865,89 @@
       <c r="P81" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R81" s="3">
         <v>319700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-227800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-272800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>260600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>144400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>332900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>576900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>473600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>205700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-717400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-808500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>318900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-348600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2433300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>570300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>688100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>841600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>740600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>910600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>809900</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>853300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>818000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>836300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>879900</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>921700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>444300</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>286400</v>
+        <v>260700</v>
       </c>
       <c r="E83" s="3">
+        <v>218300</v>
+      </c>
+      <c r="F83" s="3">
         <v>88000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>303400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>296800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>263200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>475300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>568400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>584100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>551900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>452800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>552500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>591900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>579300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>636300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1152600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1102500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>606100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>640700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>599500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>618100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>722700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>906100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>1394700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>786500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>789900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1017500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3699300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>827700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>778000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>678500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>662700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>596300</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>588300</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>616200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>611100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>583500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>590900</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>648200</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>564700</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-81100</v>
+      </c>
+      <c r="E89" s="3">
         <v>227100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-509600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>644100</v>
       </c>
-      <c r="G89" s="3">
-        <v>303000</v>
-      </c>
       <c r="H89" s="3">
+        <v>-295900</v>
+      </c>
+      <c r="I89" s="3">
         <v>-1249500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2434000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>823100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>596800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-768200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2805300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1042500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>435600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-646500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>2588400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>122200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-303400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>135300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>984600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>499900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-12600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>648000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1694000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>2183900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-1574300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>293600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3020900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>1326400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>877700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>3313800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>837800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>923100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>696200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2974200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>970400</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>943000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>1014500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2316300</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1153700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-207500</v>
+        <v>-191900</v>
       </c>
       <c r="E91" s="3">
+        <v>-171800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-381600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-327300</v>
       </c>
-      <c r="G91" s="3">
-        <v>-323000</v>
-      </c>
       <c r="H91" s="3">
-        <v>-210800</v>
+        <v>-271300</v>
       </c>
       <c r="I91" s="3">
+        <v>-168600</v>
+      </c>
+      <c r="J91" s="3">
         <v>-442100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-262100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-241100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-182300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-863300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-556700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-497800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-392200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-806400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-619800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-433000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-310000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-719300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-497000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-412100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-250200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-704700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-424200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-408700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-475600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1152100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-853700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-857200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-675900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1381900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-924800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-791900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-504400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-1183500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-714500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-735400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-625600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1217800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-834500</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-298600</v>
+        <v>-294800</v>
       </c>
       <c r="E94" s="3">
+        <v>-299800</v>
+      </c>
+      <c r="F94" s="3">
         <v>-368700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-402400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-510900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-352400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-636700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-470700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-443600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-400300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-836700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-549300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-585200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-387900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-871500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-758700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-455500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-323700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-619100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-385200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-428200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-262900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-766100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-437800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-403200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-282200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1256200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-988800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1186200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-910400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1709900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-988400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-832800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-651300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1537100</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-768200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-764900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-858400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-1626900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-889600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,52 +10455,53 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>17</v>
+      <c r="D96" s="3">
+        <v>616900</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G96" s="3">
+      <c r="F96" s="3">
+        <v>0</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H96" s="3">
         <v>587200</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
-      <c r="J96" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L96" s="3">
         <v>471400</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="O96" s="3">
+      <c r="M96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P96" s="3">
         <v>327500</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10294,11 +10528,11 @@
         <v>0</v>
       </c>
       <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-597400</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
         <v>0</v>
       </c>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,370 +10953,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-258300</v>
+        <v>-285600</v>
       </c>
       <c r="E100" s="3">
+        <v>-257100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1001500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-793100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1354100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>260500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-975300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-380300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-308600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>538400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1155100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-541900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>214000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>252100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-771700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>991900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>270400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>200100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-420700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>10900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-303000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-520900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-501700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-1615100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1889600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-818600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-158100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-130300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>293600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-272500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-287400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-429300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-270400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>415800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1023700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-488400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-190100</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-425000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>79300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-588000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-56200</v>
+        <v>-173800</v>
       </c>
       <c r="E101" s="3">
+        <v>-57300</v>
+      </c>
+      <c r="F101" s="3">
         <v>41400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-12300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-36400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-44200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>2100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-43700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-17400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-131000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>20500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>33900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>49000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-135800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>22600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>35300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>48000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>37100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>61800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-71300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-20800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-50700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>19200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-20800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>55400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>31700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-23200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-13700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-20000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-22900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-88300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>20900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>14300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-5000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-648900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-282500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1878600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-530300</v>
       </c>
-      <c r="G102" s="3">
-        <v>972400</v>
-      </c>
       <c r="H102" s="3">
-        <v>-1397500</v>
+        <v>373500</v>
       </c>
       <c r="I102" s="3">
+        <v>-1398600</v>
+      </c>
+      <c r="J102" s="3">
         <v>863400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-40200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-191800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-620300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>769300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-46600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>20700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-799700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>809400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>378000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-453200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>59600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-18200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>132600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-746900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-74000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>422100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>59700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-108400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-858300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1600100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>226500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-35600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1130200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1348200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-603000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-174000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>447000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>393400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-309100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-100200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-248000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>783000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-328900</v>
       </c>
     </row>
